--- a/data_exports/enterprise_smart_factory/Apex_Enterprise_Smart_Factory_Performance_Report.xlsx
+++ b/data_exports/enterprise_smart_factory/Apex_Enterprise_Smart_Factory_Performance_Report.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Executive Plant Performance &amp; OEE Benchmark Audit | Generated: 2026-09-14 11:13 UTC</t>
+          <t>Executive Plant Performance &amp; OEE Benchmark Audit | Generated: 2026-10-24 22:45 UTC</t>
         </is>
       </c>
     </row>
@@ -34598,7 +34598,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -35820,12 +35820,12 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -37395,12 +37395,12 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
@@ -37899,12 +37899,12 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
@@ -38214,12 +38214,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
@@ -38340,12 +38340,12 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
@@ -39348,12 +39348,12 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -39474,12 +39474,12 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -39537,12 +39537,12 @@
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
@@ -39600,12 +39600,12 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -40230,12 +40230,12 @@
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
@@ -40356,12 +40356,12 @@
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -42687,12 +42687,12 @@
       </c>
       <c r="B129" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C129" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
@@ -42939,12 +42939,12 @@
       </c>
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C133" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -43317,12 +43317,12 @@
       </c>
       <c r="B139" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C139" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -43569,12 +43569,12 @@
       </c>
       <c r="B143" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C143" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -43821,12 +43821,12 @@
       </c>
       <c r="B147" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C147" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
@@ -44955,12 +44955,12 @@
       </c>
       <c r="B165" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C165" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
@@ -45774,12 +45774,12 @@
       </c>
       <c r="B178" s="16" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C178" s="16" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D178" s="16" t="inlineStr">
@@ -45963,12 +45963,12 @@
       </c>
       <c r="B181" s="20" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="C181" s="20" t="inlineStr">
         <is>
-          <t>Siemens Continuous Hairpin Stator Inserter</t>
+          <t>Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
@@ -46193,7 +46193,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>Siemens Building X</t>
+          <t>Apex Building Systems</t>
         </is>
       </c>
       <c r="I3" s="20" t="inlineStr">
@@ -46248,7 +46248,7 @@
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>Siemens Building X</t>
+          <t>Apex Building Systems</t>
         </is>
       </c>
       <c r="I4" s="16" t="inlineStr">
@@ -46358,12 +46358,12 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>Siemens Digital Industries</t>
+          <t>Apex Industrial Automation</t>
         </is>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>SINUMERIK-Integrated</t>
+          <t>MotionPro-Integrated</t>
         </is>
       </c>
       <c r="J6" s="28" t="inlineStr">
@@ -46523,7 +46523,7 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>Siemens &amp; Comau</t>
+          <t>Apex &amp; Comau</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -46688,12 +46688,12 @@
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
-          <t>Siemens &amp; Festo</t>
+          <t>Apex &amp; Festo</t>
         </is>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
-          <t>S7-1500-Motion-Line</t>
+          <t>AX-1500-Motion-Line</t>
         </is>
       </c>
       <c r="J12" s="28" t="inlineStr">
@@ -47040,17 +47040,17 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>MCH-ZEISS-PRISMO</t>
+          <t>MCH-APEX-HAIRPIN</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>AREA-GLOBAL-QC</t>
+          <t>LINE-STG-CNC-01</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Carl Zeiss PRISMO Navigator 3D CMM</t>
+          <t xml:space="preserve">        Apex Continuous Hairpin Stator Inserter</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -47063,27 +47063,27 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Quality Lab</t>
+          <t>Powertrain Shop</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>Tier 2 (Core Production)</t>
+          <t>Tier 1 (Mission-Critical)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>Carl Zeiss Metrology</t>
+          <t>Apex Industrial Automation</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>PRISMO-9/12/7-Ultra</t>
-        </is>
-      </c>
-      <c r="J19" s="27" t="inlineStr">
-        <is>
-          <t>93.2%</t>
+          <t>ApexFlex-Stator-400</t>
+        </is>
+      </c>
+      <c r="J19" s="29" t="inlineStr">
+        <is>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="K19" s="26" t="inlineStr">
@@ -47095,17 +47095,17 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>MCH-DMG-DMC-85</t>
+          <t>MCH-ZEISS-PRISMO</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>LINE-STG-CNC-01</t>
+          <t>AREA-GLOBAL-QC</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        DMG MORI DMC 85 FD 5-Axis Mill-Turn</t>
+          <t xml:space="preserve">        Carl Zeiss PRISMO Navigator 3D CMM</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
@@ -47118,27 +47118,27 @@
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>Powertrain Shop</t>
+          <t>Quality Lab</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>Tier 1 (Mission-Critical)</t>
+          <t>Tier 2 (Core Production)</t>
         </is>
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>DMG MORI</t>
+          <t>Carl Zeiss Metrology</t>
         </is>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
-          <t>DMC-85-FD-duoBLOCK</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="inlineStr">
-        <is>
-          <t>98.3%</t>
+          <t>PRISMO-9/12/7-Ultra</t>
+        </is>
+      </c>
+      <c r="J20" s="28" t="inlineStr">
+        <is>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="K20" s="24" t="inlineStr">
@@ -47150,17 +47150,17 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>MCH-KUKA-TITAN-01</t>
+          <t>MCH-DMG-DMC-85</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>LINE-MUC-WELD-04</t>
+          <t>LINE-STG-CNC-01</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">        KUKA KR-1000 Heavy Titan Welder #1</t>
+          <t xml:space="preserve">        DMG MORI DMC 85 FD 5-Axis Mill-Turn</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -47173,7 +47173,7 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Body Shop</t>
+          <t>Powertrain Shop</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -47183,17 +47183,17 @@
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>KUKA AG</t>
+          <t>DMG MORI</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>KR-1000-titan-F</t>
-        </is>
-      </c>
-      <c r="J21" s="27" t="inlineStr">
-        <is>
-          <t>93.7%</t>
+          <t>DMC-85-FD-duoBLOCK</t>
+        </is>
+      </c>
+      <c r="J21" s="29" t="inlineStr">
+        <is>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="K21" s="26" t="inlineStr">
@@ -47205,7 +47205,7 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>MCH-KUKA-QUANT-02</t>
+          <t>MCH-KUKA-TITAN-01</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
@@ -47215,7 +47215,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        KUKA KR-210 Quantec Spot Gun #2</t>
+          <t xml:space="preserve">        KUKA KR-1000 Heavy Titan Welder #1</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -47243,12 +47243,12 @@
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>KR-210-R2700-prime</t>
-        </is>
-      </c>
-      <c r="J22" s="25" t="inlineStr">
-        <is>
-          <t>96.6%</t>
+          <t>KR-1000-titan-F</t>
+        </is>
+      </c>
+      <c r="J22" s="28" t="inlineStr">
+        <is>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="K22" s="24" t="inlineStr">
@@ -47260,17 +47260,17 @@
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>MCH-SCHULER-2500</t>
+          <t>MCH-KUKA-QUANT-02</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>LINE-MUC-PRESS-01</t>
+          <t>LINE-MUC-WELD-04</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Schuler Servo Press 2500T (Station 1)</t>
+          <t xml:space="preserve">        KUKA KR-210 Quantec Spot Gun #2</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -47283,7 +47283,7 @@
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Stamping Shop</t>
+          <t>Body Shop</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -47293,17 +47293,17 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>Schuler AG</t>
+          <t>KUKA AG</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>MSD2-2500-Servo</t>
+          <t>KR-210-R2700-prime</t>
         </is>
       </c>
       <c r="J23" s="29" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K23" s="26" t="inlineStr">
@@ -47315,17 +47315,17 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>MCH-SIEMENS-HAIRPIN</t>
+          <t>MCH-SCHULER-2500</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>LINE-STG-CNC-01</t>
+          <t>LINE-MUC-PRESS-01</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Siemens Continuous Hairpin Stator Inserter</t>
+          <t xml:space="preserve">        Schuler Servo Press 2500T (Station 1)</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -47338,7 +47338,7 @@
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>Powertrain Shop</t>
+          <t>Stamping Shop</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
@@ -47348,17 +47348,17 @@
       </c>
       <c r="H24" s="16" t="inlineStr">
         <is>
-          <t>Siemens Digital Industries</t>
+          <t>Schuler AG</t>
         </is>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
-          <t>SIMATIC-StatorFlex-400</t>
+          <t>MSD2-2500-Servo</t>
         </is>
       </c>
       <c r="J24" s="25" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K24" s="24" t="inlineStr">
@@ -47733,7 +47733,7 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>Siemens SIPLUS CMS</t>
+          <t>Apex VibSense CMS</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -47788,12 +47788,12 @@
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>Siemens SINAMICS</t>
+          <t>Apex DriveTech</t>
         </is>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
-          <t>S120-LEM-Sensor</t>
+          <t>AX120-LEM-Sensor</t>
         </is>
       </c>
       <c r="J32" s="25" t="inlineStr">
